--- a/datos/costos.xlsx
+++ b/datos/costos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APP BOLIS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pagina Venta Bolis\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A0DB05-4690-4E5A-9F7A-7E77F59BA45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E63A280-7B18-4508-94BC-BFA59F2AB1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="585" yWindow="930" windowWidth="21570" windowHeight="13035" tabRatio="695" xr2:uid="{C9F31BEF-597D-471C-872A-5048C5703FC4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="695" xr2:uid="{C9F31BEF-597D-471C-872A-5048C5703FC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sabores 2025" sheetId="11" r:id="rId1"/>
@@ -1056,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2EAEE6-23BA-467B-8FCC-6B86426A06BE}">
-  <dimension ref="A1:T137"/>
+  <dimension ref="A1:Q137"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
@@ -1065,18 +1065,16 @@
     <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" customWidth="1"/>
+    <col min="8" max="8" width="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="46" t="s">
         <v>16</v>
       </c>
@@ -1086,16 +1084,16 @@
       <c r="E1" s="47"/>
       <c r="F1" s="48"/>
       <c r="G1" s="2"/>
-      <c r="K1" s="50" t="s">
+      <c r="H1" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="52"/>
-      <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="52"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>49</v>
       </c>
@@ -1114,67 +1112,67 @@
       <c r="F2" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="I2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="J2" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="K2" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="L2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="P2" t="s">
+      <c r="M2" t="s">
         <v>55</v>
       </c>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="str">
-        <f>K3</f>
+        <f>H3</f>
         <v>Leche entera</v>
       </c>
       <c r="B3" s="27">
         <v>1</v>
       </c>
       <c r="C3" s="7">
-        <f>L3</f>
+        <f>I3</f>
         <v>1.5</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>62</v>
       </c>
       <c r="E3" s="21">
-        <f>N3</f>
+        <f>K3</f>
         <v>30</v>
       </c>
       <c r="F3" s="24">
         <f>E3*B3</f>
         <v>30</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="7">
+      <c r="I3" s="7">
         <v>1.5</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="N3" s="8">
+      <c r="K3" s="8">
         <v>30</v>
       </c>
-      <c r="O3" s="10"/>
-      <c r="T3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L3" s="10"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="str">
-        <f>K7</f>
+        <f>H7</f>
         <v>Vainilla</v>
       </c>
       <c r="B4" s="27">
@@ -1187,107 +1185,107 @@
         <v>40</v>
       </c>
       <c r="E4" s="21">
-        <f>N7</f>
+        <f>K7</f>
         <v>18.5</v>
       </c>
       <c r="F4" s="24">
-        <f>(N7/L7)*C4</f>
+        <f>(K7/I7)*C4</f>
         <v>3.7</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="7">
+      <c r="I4" s="7">
         <v>180</v>
       </c>
-      <c r="M4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="8">
+      <c r="J4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="8">
         <v>58</v>
       </c>
-      <c r="O4" s="10"/>
-      <c r="T4" s="1"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L4" s="10"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="str">
-        <f>K4</f>
+        <f>H4</f>
         <v>CMC</v>
       </c>
       <c r="B5" s="27">
         <v>7.5</v>
       </c>
       <c r="C5" s="7">
-        <f>L4</f>
+        <f>I4</f>
         <v>180</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="21">
-        <f>N4</f>
+        <f>K4</f>
         <v>58</v>
       </c>
       <c r="F5" s="24">
         <f>(E5/C5)*B5</f>
         <v>2.416666666666667</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="7">
+      <c r="I5" s="7">
         <v>380</v>
       </c>
-      <c r="M5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" s="8">
+      <c r="J5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="8">
         <v>29</v>
       </c>
-      <c r="O5" s="11">
+      <c r="L5" s="11">
         <v>20</v>
       </c>
-      <c r="T5" s="1"/>
-    </row>
-    <row r="6" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="32" t="str">
-        <f>K5</f>
+        <f>H5</f>
         <v>Leche condensada</v>
       </c>
       <c r="B6" s="33">
         <v>1.5</v>
       </c>
       <c r="C6" s="34">
-        <f>L5</f>
+        <f>I5</f>
         <v>380</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="35">
-        <f>N5</f>
+        <f>K5</f>
         <v>29</v>
       </c>
       <c r="F6" s="24">
         <f>E6*B6</f>
         <v>43.5</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="7">
+      <c r="I6" s="7">
         <v>1</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="8">
+      <c r="K6" s="8">
         <v>60</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="T6" s="1"/>
-    </row>
-    <row r="7" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L6" s="10"/>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1304,62 +1302,61 @@
         <f>SUM(F3:F6)</f>
         <v>79.616666666666674</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="7">
+      <c r="I7" s="7">
         <v>150</v>
       </c>
-      <c r="M7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N7" s="8">
+      <c r="J7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="8">
         <v>18.5</v>
       </c>
-      <c r="O7" s="10"/>
-      <c r="T7" s="1"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L7" s="10"/>
+      <c r="Q7" s="1"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F8" s="2"/>
-      <c r="H8" s="1"/>
-      <c r="K8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="7">
+      <c r="I8" s="7">
         <v>24</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="N8" s="8">
+      <c r="K8" s="8">
         <v>37</v>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" t="s">
+      <c r="L8" s="10"/>
+      <c r="M8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="49"/>
       <c r="B9" s="49"/>
-      <c r="K9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L9" s="7">
+      <c r="I9" s="7">
         <v>432</v>
       </c>
-      <c r="M9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N9" s="8">
+      <c r="J9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="8">
         <v>38</v>
       </c>
-      <c r="O9" s="10"/>
-      <c r="P9" t="s">
+      <c r="L9" s="10"/>
+      <c r="M9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A10" s="46" t="s">
         <v>58</v>
       </c>
@@ -1369,21 +1366,21 @@
       <c r="E10" s="47"/>
       <c r="F10" s="48"/>
       <c r="G10" s="1"/>
-      <c r="K10" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="7">
-        <v>13</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N10" s="8">
+      <c r="I10" s="7">
+        <v>13</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="8">
         <v>6.5</v>
       </c>
-      <c r="O10" s="10"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L10" s="10"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>49</v>
       </c>
@@ -1402,23 +1399,23 @@
       <c r="F11" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="7">
-        <v>13</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N11" s="8">
+      <c r="I11" s="7">
+        <v>13</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="8">
         <v>5.8</v>
       </c>
-      <c r="O11" s="10"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L11" s="10"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="str">
-        <f>K6</f>
+        <f>H6</f>
         <v>Ciruela cocida</v>
       </c>
       <c r="B12" s="27">
@@ -1431,30 +1428,30 @@
         <v>52</v>
       </c>
       <c r="E12" s="21">
-        <f>N6</f>
+        <f>K6</f>
         <v>60</v>
       </c>
       <c r="F12" s="24">
         <f>E12*B12</f>
         <v>60</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L12" s="7">
-        <v>13</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N12" s="8">
+      <c r="I12" s="7">
+        <v>13</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="8">
         <v>5.8</v>
       </c>
-      <c r="O12" s="10"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L12" s="10"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="str">
-        <f>K5</f>
+        <f>H5</f>
         <v>Leche condensada</v>
       </c>
       <c r="B13" s="27">
@@ -1464,32 +1461,32 @@
         <v>380</v>
       </c>
       <c r="D13" s="7" t="str">
-        <f>M5</f>
+        <f>J5</f>
         <v>grs</v>
       </c>
       <c r="E13" s="21">
-        <f>N5</f>
+        <f>K5</f>
         <v>29</v>
       </c>
       <c r="F13" s="24">
         <f>E13*B13</f>
         <v>14.5</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="7">
+      <c r="I13" s="7">
         <v>255</v>
       </c>
-      <c r="M13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N13" s="8">
+      <c r="J13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="8">
         <v>56</v>
       </c>
-      <c r="O13" s="10"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="L13" s="10"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="str">
         <f>$A$1</f>
         <v>Preparacion base de leche</v>
@@ -1512,21 +1509,21 @@
         <f>$F$7</f>
         <v>79.616666666666674</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L14" s="7">
+      <c r="I14" s="7">
         <v>1</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="J14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N14" s="8">
+      <c r="K14" s="8">
         <v>20</v>
       </c>
-      <c r="O14" s="10"/>
-    </row>
-    <row r="15" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="10"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>47</v>
       </c>
@@ -1540,28 +1537,28 @@
         <v>13</v>
       </c>
       <c r="E15" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F15" s="26">
         <f>E15*C15</f>
         <v>16.289909999999999</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L15" s="7">
+      <c r="I15" s="7">
         <v>2</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="J15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N15" s="8">
+      <c r="K15" s="8">
         <v>183</v>
       </c>
-      <c r="O15" s="10"/>
-    </row>
-    <row r="16" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="10"/>
+    </row>
+    <row r="16" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>17</v>
       </c>
@@ -1573,21 +1570,21 @@
         <f>SUM(F12:F15)</f>
         <v>170.40657666666667</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="H16" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L16" s="7">
+      <c r="I16" s="7">
         <v>47</v>
       </c>
-      <c r="M16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N16" s="8">
+      <c r="J16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="8">
         <v>14.2</v>
       </c>
-      <c r="O16" s="10"/>
-    </row>
-    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L16" s="10"/>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>51</v>
       </c>
@@ -1599,21 +1596,21 @@
         <f>B15</f>
         <v>14</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="7">
+      <c r="I17" s="7">
         <v>47</v>
       </c>
-      <c r="M17" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N17" s="8">
+      <c r="J17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="8">
         <v>14.3</v>
       </c>
-      <c r="O17" s="10"/>
-    </row>
-    <row r="18" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="10"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1625,7 +1622,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="6">
-        <f>$L$26</f>
+        <f>$I$26</f>
         <v>25</v>
       </c>
       <c r="E18" s="31" t="s">
@@ -1636,21 +1633,21 @@
         <v>12.828101666666667</v>
       </c>
       <c r="G18" s="37"/>
-      <c r="K18" s="9" t="s">
+      <c r="H18" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="7">
+      <c r="I18" s="7">
         <v>1</v>
       </c>
-      <c r="M18" s="7" t="s">
+      <c r="J18" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="N18" s="8">
+      <c r="K18" s="8">
         <v>577</v>
       </c>
-      <c r="O18" s="10"/>
-    </row>
-    <row r="19" spans="1:15" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="L18" s="10"/>
+    </row>
+    <row r="19" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="38" t="s">
         <v>64</v>
       </c>
@@ -1662,36 +1659,36 @@
         <f>((D18-B18)/D18)</f>
         <v>0.51312406666666666</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L19" s="7">
+      <c r="I19" s="7">
         <v>100</v>
       </c>
-      <c r="M19" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N19" s="8">
+      <c r="J19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="8">
         <v>25</v>
       </c>
-      <c r="O19" s="10"/>
-    </row>
-    <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K20" s="9" t="s">
+      <c r="L19" s="10"/>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H20" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L20" s="7">
+      <c r="I20" s="7">
         <v>1</v>
       </c>
-      <c r="M20" s="7" t="s">
+      <c r="J20" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="8">
+      <c r="K20" s="8">
         <v>24</v>
       </c>
-      <c r="O20" s="10"/>
-    </row>
-    <row r="21" spans="1:15" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="L20" s="10"/>
+    </row>
+    <row r="21" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A21" s="46" t="s">
         <v>59</v>
       </c>
@@ -1700,21 +1697,21 @@
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
-      <c r="K21" s="9" t="s">
+      <c r="H21" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L21" s="7">
+      <c r="I21" s="7">
         <v>120</v>
       </c>
-      <c r="M21" s="7" t="s">
+      <c r="J21" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="N21" s="8">
+      <c r="K21" s="8">
         <v>44</v>
       </c>
-      <c r="O21" s="10"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L21" s="10"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
         <v>49</v>
       </c>
@@ -1733,24 +1730,23 @@
       <c r="F22" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="H22" s="2"/>
-      <c r="K22" s="9" t="s">
+      <c r="H22" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L22" s="7">
+      <c r="I22" s="7">
         <v>1</v>
       </c>
-      <c r="M22" s="7" t="s">
+      <c r="J22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N22" s="8">
+      <c r="K22" s="8">
         <v>119</v>
       </c>
-      <c r="O22" s="10"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L22" s="10"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="str">
-        <f>K15</f>
+        <f>H15</f>
         <v>Fresas congelada</v>
       </c>
       <c r="B23" s="27">
@@ -1769,23 +1765,23 @@
         <f>E23*B23</f>
         <v>16</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="H23" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="L23" s="7">
+      <c r="I23" s="7">
         <v>500</v>
       </c>
-      <c r="M23" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N23" s="8">
+      <c r="J23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="8">
         <v>60</v>
       </c>
-      <c r="O23" s="10"/>
-    </row>
-    <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L23" s="10"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="str">
-        <f>K12</f>
+        <f>H12</f>
         <v>Sobre de tang fresa</v>
       </c>
       <c r="B24" s="27">
@@ -1798,28 +1794,28 @@
         <v>13</v>
       </c>
       <c r="E24" s="21">
-        <f>N12</f>
+        <f>K12</f>
         <v>5.8</v>
       </c>
       <c r="F24" s="24">
         <f>E24*B24</f>
         <v>5.8</v>
       </c>
-      <c r="K24" s="12" t="s">
+      <c r="H24" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="L24" s="13">
+      <c r="I24" s="13">
         <v>1</v>
       </c>
-      <c r="M24" s="13" t="s">
+      <c r="J24" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="N24" s="14">
+      <c r="K24" s="14">
         <v>25</v>
       </c>
-      <c r="O24" s="15"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L24" s="15"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="str">
         <f>$A$1</f>
         <v>Preparacion base de leche</v>
@@ -1843,7 +1839,7 @@
         <v>79.616666666666674</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>47</v>
       </c>
@@ -1857,21 +1853,21 @@
         <v>13</v>
       </c>
       <c r="E26" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F26" s="26">
         <f>E26*C26</f>
         <v>16.289909999999999</v>
       </c>
-      <c r="K26" t="s">
+      <c r="H26" t="s">
         <v>63</v>
       </c>
-      <c r="L26" s="1">
+      <c r="I26" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>17</v>
       </c>
@@ -1884,7 +1880,7 @@
         <v>117.70657666666668</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>51</v>
       </c>
@@ -1898,7 +1894,7 @@
       </c>
       <c r="G28" s="37"/>
     </row>
-    <row r="29" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>4</v>
       </c>
@@ -1910,7 +1906,7 @@
         <v>5</v>
       </c>
       <c r="D29" s="6">
-        <f>$L$26</f>
+        <f>$I$26</f>
         <v>25</v>
       </c>
       <c r="E29" s="31" t="s">
@@ -1922,7 +1918,7 @@
       </c>
       <c r="G29" s="37"/>
     </row>
-    <row r="30" spans="1:15" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="38" t="s">
         <v>64</v>
       </c>
@@ -1935,10 +1931,10 @@
         <v>0.60764474444444438</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="30"/>
     </row>
-    <row r="32" spans="1:15" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A32" s="46" t="s">
         <v>53</v>
       </c>
@@ -1970,7 +1966,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="str">
-        <f>$K$9</f>
+        <f>$H$9</f>
         <v>Galleta maria</v>
       </c>
       <c r="B34" s="27">
@@ -1983,7 +1979,7 @@
         <v>13</v>
       </c>
       <c r="E34" s="21">
-        <f>N9/3</f>
+        <f>K9/3</f>
         <v>12.666666666666666</v>
       </c>
       <c r="F34" s="24">
@@ -2029,7 +2025,7 @@
         <v>13</v>
       </c>
       <c r="E36" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F36" s="26">
@@ -2076,7 +2072,7 @@
         <v>5</v>
       </c>
       <c r="D39" s="6">
-        <f>$L$26</f>
+        <f>$I$26</f>
         <v>25</v>
       </c>
       <c r="E39" s="31" t="s">
@@ -2134,7 +2130,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="str">
-        <f>K8</f>
+        <f>H8</f>
         <v>Galleta oreo</v>
       </c>
       <c r="B44" s="27">
@@ -2147,7 +2143,7 @@
         <v>13</v>
       </c>
       <c r="E44" s="21">
-        <f>N9/24</f>
+        <f>K9/24</f>
         <v>1.5833333333333333</v>
       </c>
       <c r="F44" s="24">
@@ -2193,7 +2189,7 @@
         <v>13</v>
       </c>
       <c r="E46" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F46" s="26">
@@ -2228,7 +2224,7 @@
       </c>
       <c r="G48" s="37"/>
     </row>
-    <row r="49" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2240,7 +2236,7 @@
         <v>5</v>
       </c>
       <c r="D49" s="6">
-        <f>$L$26</f>
+        <f>$I$26</f>
         <v>25</v>
       </c>
       <c r="E49" s="31" t="s">
@@ -2252,7 +2248,7 @@
       </c>
       <c r="G49" s="37"/>
     </row>
-    <row r="50" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:7" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="38" t="s">
         <v>64</v>
       </c>
@@ -2264,11 +2260,9 @@
         <f>((D49-B49)/D49)</f>
         <v>0.61170029999999997</v>
       </c>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-    </row>
-    <row r="51" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+    </row>
+    <row r="51" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A52" s="46" t="s">
         <v>1</v>
       </c>
@@ -2278,7 +2272,7 @@
       <c r="E52" s="47"/>
       <c r="F52" s="48"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="22" t="s">
         <v>49</v>
       </c>
@@ -2298,9 +2292,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="str">
-        <f>K16</f>
+        <f>H16</f>
         <v>Maicena nuez</v>
       </c>
       <c r="B54" s="27">
@@ -2313,7 +2307,7 @@
         <v>13</v>
       </c>
       <c r="E54" s="21">
-        <f>N16</f>
+        <f>K16</f>
         <v>14.2</v>
       </c>
       <c r="F54" s="24">
@@ -2321,7 +2315,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="str">
         <f>$A$1</f>
         <v>Preparacion base de leche</v>
@@ -2345,7 +2339,7 @@
         <v>79.616666666666674</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>47</v>
       </c>
@@ -2359,7 +2353,7 @@
         <v>13</v>
       </c>
       <c r="E56" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F56" s="26">
@@ -2367,7 +2361,7 @@
         <v>16.289909999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>17</v>
       </c>
@@ -2380,7 +2374,7 @@
         <v>110.10657666666668</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>51</v>
       </c>
@@ -2394,7 +2388,7 @@
       </c>
       <c r="G58" s="37"/>
     </row>
-    <row r="59" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2406,7 +2400,7 @@
         <v>5</v>
       </c>
       <c r="D59" s="6">
-        <f>$L$26</f>
+        <f>$I$26</f>
         <v>25</v>
       </c>
       <c r="E59" s="31" t="s">
@@ -2418,7 +2412,7 @@
       </c>
       <c r="G59" s="37"/>
     </row>
-    <row r="60" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:7" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="38" t="s">
         <v>64</v>
       </c>
@@ -2431,8 +2425,8 @@
         <v>0.6329780777777777</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:7" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A62" s="46" t="s">
         <v>9</v>
       </c>
@@ -2442,7 +2436,7 @@
       <c r="E62" s="47"/>
       <c r="F62" s="48"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="22" t="s">
         <v>49</v>
       </c>
@@ -2462,23 +2456,23 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="str">
-        <f>K17</f>
+        <f>H17</f>
         <v>Maicena coco</v>
       </c>
       <c r="B64" s="27">
         <v>1</v>
       </c>
       <c r="C64" s="7">
-        <f>L17</f>
+        <f>I17</f>
         <v>47</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="21">
-        <f>N17</f>
+        <f>K17</f>
         <v>14.3</v>
       </c>
       <c r="F64" s="24">
@@ -2486,7 +2480,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="str">
         <f>$A$1</f>
         <v>Preparacion base de leche</v>
@@ -2510,7 +2504,7 @@
         <v>79.616666666666674</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
         <v>47</v>
       </c>
@@ -2524,7 +2518,7 @@
         <v>13</v>
       </c>
       <c r="E66" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F66" s="26">
@@ -2532,7 +2526,7 @@
         <v>16.289909999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>17</v>
       </c>
@@ -2545,7 +2539,7 @@
         <v>110.20657666666668</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>51</v>
       </c>
@@ -2559,7 +2553,7 @@
       </c>
       <c r="G68" s="37"/>
     </row>
-    <row r="69" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>4</v>
       </c>
@@ -2571,7 +2565,7 @@
         <v>5</v>
       </c>
       <c r="D69" s="6">
-        <f>$L$26</f>
+        <f>$I$26</f>
         <v>25</v>
       </c>
       <c r="E69" s="31" t="s">
@@ -2583,7 +2577,7 @@
       </c>
       <c r="G69" s="37"/>
     </row>
-    <row r="70" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="38" t="s">
         <v>64</v>
       </c>
@@ -2596,8 +2590,8 @@
         <v>0.63264474444444441</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="72" spans="1:11" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A72" s="46" t="s">
         <v>2</v>
       </c>
@@ -2607,7 +2601,7 @@
       <c r="E72" s="47"/>
       <c r="F72" s="48"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
         <v>49</v>
       </c>
@@ -2627,9 +2621,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="str">
-        <f>K21</f>
+        <f>H21</f>
         <v>Vainilla para helados</v>
       </c>
       <c r="B74" s="27">
@@ -2642,7 +2636,7 @@
         <v>61</v>
       </c>
       <c r="E74" s="21">
-        <f>N21/4</f>
+        <f>K21/4</f>
         <v>11</v>
       </c>
       <c r="F74" s="24">
@@ -2650,7 +2644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="str">
         <f>$A$1</f>
         <v>Preparacion base de leche</v>
@@ -2674,7 +2668,7 @@
         <v>79.616666666666674</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>47</v>
       </c>
@@ -2688,7 +2682,7 @@
         <v>13</v>
       </c>
       <c r="E76" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F76" s="26">
@@ -2696,7 +2690,7 @@
         <v>16.289909999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>17</v>
       </c>
@@ -2709,7 +2703,7 @@
         <v>106.90657666666667</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>51</v>
       </c>
@@ -2723,7 +2717,7 @@
       </c>
       <c r="G78" s="37"/>
     </row>
-    <row r="79" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>4</v>
       </c>
@@ -2735,7 +2729,7 @@
         <v>5</v>
       </c>
       <c r="D79" s="6">
-        <f>$L$26</f>
+        <f>$I$26</f>
         <v>25</v>
       </c>
       <c r="E79" s="31" t="s">
@@ -2745,9 +2739,9 @@
         <f>D79-B79</f>
         <v>16.091118611111114</v>
       </c>
-      <c r="K79" s="1"/>
-    </row>
-    <row r="80" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H79" s="1"/>
+    </row>
+    <row r="80" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="38" t="s">
         <v>64</v>
       </c>
@@ -2793,7 +2787,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="str">
-        <f>K18</f>
+        <f>H18</f>
         <v>Baileys</v>
       </c>
       <c r="B84" s="27">
@@ -2806,7 +2800,7 @@
         <v>42</v>
       </c>
       <c r="E84" s="21">
-        <f>N18</f>
+        <f>K18</f>
         <v>577</v>
       </c>
       <c r="F84" s="24">
@@ -2852,7 +2846,7 @@
         <v>13</v>
       </c>
       <c r="E86" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F86" s="26">
@@ -2954,7 +2948,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="9" t="str">
-        <f>$K$20</f>
+        <f>$H$20</f>
         <v>Azúcar</v>
       </c>
       <c r="B94" s="27">
@@ -3012,7 +3006,7 @@
         <v>13</v>
       </c>
       <c r="E96" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F96" s="26">
@@ -3020,7 +3014,7 @@
         <v>16.289909999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>17</v>
       </c>
@@ -3033,7 +3027,7 @@
         <v>104.18657666666667</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>51</v>
       </c>
@@ -3046,7 +3040,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>4</v>
       </c>
@@ -3058,7 +3052,7 @@
         <v>5</v>
       </c>
       <c r="D99" s="6">
-        <f>$L$26</f>
+        <f>$I$26</f>
         <v>25</v>
       </c>
       <c r="E99" s="31" t="s">
@@ -3069,7 +3063,7 @@
         <v>16.31778527777778</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="38" t="s">
         <v>64</v>
       </c>
@@ -3082,8 +3076,8 @@
         <v>0.65271141111111119</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="102" spans="1:11" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="1:8" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A102" s="46" t="s">
         <v>65</v>
       </c>
@@ -3093,7 +3087,7 @@
       <c r="E102" s="47"/>
       <c r="F102" s="48"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="22" t="s">
         <v>49</v>
       </c>
@@ -3112,11 +3106,11 @@
       <c r="F103" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="K103" s="1"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H103" s="1"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="str">
-        <f>$K$20</f>
+        <f>$H$20</f>
         <v>Azúcar</v>
       </c>
       <c r="B104" s="27">
@@ -3135,11 +3129,11 @@
         <f>(E104/C104)*B104</f>
         <v>8.2799999999999994</v>
       </c>
-      <c r="K104" s="1"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H104" s="1"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="str">
-        <f>K14</f>
+        <f>H14</f>
         <v>Mango</v>
       </c>
       <c r="B105" s="27">
@@ -3152,32 +3146,32 @@
         <v>13</v>
       </c>
       <c r="E105" s="21">
-        <f>N14</f>
+        <f>K14</f>
         <v>20</v>
       </c>
       <c r="F105" s="24">
         <f>(E105/C105)*B105</f>
         <v>10</v>
       </c>
-      <c r="K105" s="1"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H105" s="1"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="32" t="str">
-        <f>K11</f>
+        <f>H11</f>
         <v>Sobre de tang mango</v>
       </c>
       <c r="B106" s="33">
         <v>6.5</v>
       </c>
       <c r="C106" s="34">
-        <f>L11</f>
+        <f>I11</f>
         <v>13</v>
       </c>
       <c r="D106" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E106" s="41">
-        <f>N11</f>
+        <f>K11</f>
         <v>5.8</v>
       </c>
       <c r="F106" s="24">
@@ -3185,23 +3179,23 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="32" t="str">
-        <f>K13</f>
+        <f>H13</f>
         <v>Tajin</v>
       </c>
       <c r="B107" s="33">
         <v>30</v>
       </c>
       <c r="C107" s="34">
-        <f>L13</f>
+        <f>I13</f>
         <v>255</v>
       </c>
       <c r="D107" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E107" s="41">
-        <f>N13</f>
+        <f>K13</f>
         <v>56</v>
       </c>
       <c r="F107" s="24">
@@ -3209,23 +3203,23 @@
         <v>6.5882352941176467</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="str">
-        <f>$K$4</f>
+        <f>$H$4</f>
         <v>CMC</v>
       </c>
       <c r="B108" s="27">
         <v>7.5</v>
       </c>
       <c r="C108" s="7">
-        <f>L4</f>
+        <f>I4</f>
         <v>180</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E108" s="21">
-        <f>N4</f>
+        <f>K4</f>
         <v>58</v>
       </c>
       <c r="F108" s="24">
@@ -3233,7 +3227,7 @@
         <v>2.416666666666667</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="32" t="s">
         <v>0</v>
       </c>
@@ -3253,7 +3247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="12" t="s">
         <v>47</v>
       </c>
@@ -3267,7 +3261,7 @@
         <v>13</v>
       </c>
       <c r="E110" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F110" s="26">
@@ -3275,7 +3269,7 @@
         <v>16.289909999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>17</v>
       </c>
@@ -3288,7 +3282,7 @@
         <v>51.474811960784315</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>51</v>
       </c>
@@ -3369,20 +3363,20 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="32" t="str">
+        <f>H10</f>
+        <v>Sobre de tang limon</v>
+      </c>
+      <c r="B118" s="33">
+        <v>13</v>
+      </c>
+      <c r="C118" s="34">
+        <v>13</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="41">
         <f>K10</f>
-        <v>Sobre de tang limon</v>
-      </c>
-      <c r="B118" s="33">
-        <v>13</v>
-      </c>
-      <c r="C118" s="34">
-        <v>13</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="41">
-        <f>N10</f>
         <v>6.5</v>
       </c>
       <c r="F118" s="24">
@@ -3392,7 +3386,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="9" t="str">
-        <f>$K$20</f>
+        <f>$H$20</f>
         <v>Azúcar</v>
       </c>
       <c r="B119" s="27">
@@ -3434,21 +3428,21 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="str">
-        <f>$K$4</f>
+        <f>$H$4</f>
         <v>CMC</v>
       </c>
       <c r="B121" s="27">
         <v>7.5</v>
       </c>
       <c r="C121" s="7">
-        <f>L17</f>
+        <f>I17</f>
         <v>47</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E121" s="21">
-        <f>N17</f>
+        <f>K17</f>
         <v>14.3</v>
       </c>
       <c r="F121" s="24">
@@ -3470,7 +3464,7 @@
         <v>13</v>
       </c>
       <c r="E122" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F122" s="26">
@@ -3572,7 +3566,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="str">
-        <f>$K$9</f>
+        <f>$H$9</f>
         <v>Galleta maria</v>
       </c>
       <c r="B130" s="27">
@@ -3585,7 +3579,7 @@
         <v>13</v>
       </c>
       <c r="E130" s="21">
-        <f>N9/3</f>
+        <f>K9/3</f>
         <v>12.666666666666666</v>
       </c>
       <c r="F130" s="24">
@@ -3595,11 +3589,11 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="9" t="str">
-        <f>K10</f>
+        <f>H10</f>
         <v>Sobre de tang limon</v>
       </c>
       <c r="B131" s="27">
-        <f>L10</f>
+        <f>I10</f>
         <v>13</v>
       </c>
       <c r="C131" s="7">
@@ -3610,7 +3604,7 @@
         <v>13</v>
       </c>
       <c r="E131" s="41">
-        <f>N10</f>
+        <f>K10</f>
         <v>6.5</v>
       </c>
       <c r="F131" s="24">
@@ -3656,7 +3650,7 @@
         <v>13</v>
       </c>
       <c r="E133" s="25">
-        <f xml:space="preserve"> $N$22 / 1000 * 11.7</f>
+        <f xml:space="preserve"> $K$22 / 1000 * 11.7</f>
         <v>1.3922999999999999</v>
       </c>
       <c r="F133" s="26">
@@ -3702,7 +3696,7 @@
         <v>5</v>
       </c>
       <c r="D136" s="6">
-        <f>$L$26</f>
+        <f>$I$26</f>
         <v>25</v>
       </c>
       <c r="E136" s="31" t="s">
@@ -3728,21 +3722,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="K1:O1"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A116:F116"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
